--- a/Speciallægeloft/speciallægeloft_data/hospitaler_loft.xlsx
+++ b/Speciallægeloft/speciallægeloft_data/hospitaler_loft.xlsx
@@ -67,7 +67,7 @@
     <t>Datasæt 12 2025</t>
   </si>
   <si>
-    <t>Kørsel 15.4.2026 13.04.24</t>
+    <t>Kørsel 15.4.2026 14.35.09</t>
   </si>
   <si>
     <t/>
